--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309429</v>
+        <v>122309226</v>
       </c>
       <c r="B2" t="n">
-        <v>94947</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339028</v>
+        <v>339035</v>
       </c>
       <c r="R2" t="n">
-        <v>6394151</v>
+        <v>6394234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309226</v>
+        <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>95764</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339035</v>
+        <v>338985</v>
       </c>
       <c r="R3" t="n">
-        <v>6394234</v>
+        <v>6394264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309061</v>
+        <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>95764</v>
+        <v>94947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338985</v>
+        <v>339028</v>
       </c>
       <c r="R4" t="n">
-        <v>6394264</v>
+        <v>6394151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309226</v>
+        <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>94957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339035</v>
+        <v>339028</v>
       </c>
       <c r="R2" t="n">
-        <v>6394234</v>
+        <v>6394151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +780,7 @@
         <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>95764</v>
+        <v>95774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309429</v>
+        <v>122309226</v>
       </c>
       <c r="B4" t="n">
-        <v>94947</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339028</v>
+        <v>339035</v>
       </c>
       <c r="R4" t="n">
-        <v>6394151</v>
+        <v>6394234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309429</v>
+        <v>122309226</v>
       </c>
       <c r="B2" t="n">
-        <v>94957</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339028</v>
+        <v>339035</v>
       </c>
       <c r="R2" t="n">
-        <v>6394151</v>
+        <v>6394234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309226</v>
+        <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>94957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339035</v>
+        <v>339028</v>
       </c>
       <c r="R4" t="n">
-        <v>6394234</v>
+        <v>6394151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122309226</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>95774</v>
+        <v>95786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>122355435</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309226</v>
+        <v>122309061</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>95791</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339035</v>
+        <v>338985</v>
       </c>
       <c r="R2" t="n">
-        <v>6394234</v>
+        <v>6394264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309061</v>
+        <v>122309226</v>
       </c>
       <c r="B3" t="n">
-        <v>95786</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338985</v>
+        <v>339035</v>
       </c>
       <c r="R3" t="n">
-        <v>6394264</v>
+        <v>6394234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
         <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122309061</v>
       </c>
       <c r="B2" t="n">
-        <v>95791</v>
+        <v>95800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>2590</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kornknutmossa</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>100049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -887,7 +877,7 @@
         <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,11 +891,6 @@
       </c>
       <c r="E4" t="n">
         <v>2180</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1003,11 +988,6 @@
       </c>
       <c r="E5" t="n">
         <v>106554</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309061</v>
+        <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>95800</v>
+        <v>94983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338985</v>
+        <v>339028</v>
       </c>
       <c r="R2" t="n">
-        <v>6394264</v>
+        <v>6394151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309226</v>
+        <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>95800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,38 +784,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339035</v>
+        <v>338985</v>
       </c>
       <c r="R3" t="n">
-        <v>6394234</v>
+        <v>6394264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309429</v>
+        <v>122309226</v>
       </c>
       <c r="B4" t="n">
-        <v>94983</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,33 +881,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339028</v>
+        <v>339035</v>
       </c>
       <c r="R4" t="n">
-        <v>6394151</v>
+        <v>6394234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309429</v>
+        <v>122309061</v>
       </c>
       <c r="B2" t="n">
-        <v>94983</v>
+        <v>95800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339028</v>
+        <v>338985</v>
       </c>
       <c r="R2" t="n">
-        <v>6394151</v>
+        <v>6394264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309061</v>
+        <v>122309226</v>
       </c>
       <c r="B3" t="n">
-        <v>95800</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,33 +784,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338985</v>
+        <v>339035</v>
       </c>
       <c r="R3" t="n">
-        <v>6394264</v>
+        <v>6394234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309226</v>
+        <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>94983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -881,38 +886,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339035</v>
+        <v>339028</v>
       </c>
       <c r="R4" t="n">
-        <v>6394234</v>
+        <v>6394151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122309061</v>
       </c>
       <c r="B2" t="n">
-        <v>95800</v>
+        <v>95813</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>2590</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309226</v>
+        <v>122309429</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>94996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339035</v>
+        <v>339028</v>
       </c>
       <c r="R3" t="n">
-        <v>6394234</v>
+        <v>6394151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309429</v>
+        <v>122309226</v>
       </c>
       <c r="B4" t="n">
-        <v>94983</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,33 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339028</v>
+        <v>339035</v>
       </c>
       <c r="R4" t="n">
-        <v>6394151</v>
+        <v>6394234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,6 +1003,11 @@
       </c>
       <c r="E5" t="n">
         <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309061</v>
+        <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>95813</v>
+        <v>95009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338985</v>
+        <v>339028</v>
       </c>
       <c r="R2" t="n">
-        <v>6394264</v>
+        <v>6394151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309429</v>
+        <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>95826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339028</v>
+        <v>338985</v>
       </c>
       <c r="R3" t="n">
-        <v>6394151</v>
+        <v>6394264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309061</v>
+        <v>122309226</v>
       </c>
       <c r="B3" t="n">
-        <v>95826</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338985</v>
+        <v>339035</v>
       </c>
       <c r="R3" t="n">
-        <v>6394264</v>
+        <v>6394234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309226</v>
+        <v>122309061</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>95826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339035</v>
+        <v>338985</v>
       </c>
       <c r="R4" t="n">
-        <v>6394234</v>
+        <v>6394264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309429</v>
+        <v>122309061</v>
       </c>
       <c r="B2" t="n">
-        <v>95009</v>
+        <v>95828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339028</v>
+        <v>338985</v>
       </c>
       <c r="R2" t="n">
-        <v>6394151</v>
+        <v>6394264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309061</v>
+        <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>95826</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338985</v>
+        <v>339028</v>
       </c>
       <c r="R4" t="n">
-        <v>6394264</v>
+        <v>6394151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309061</v>
+        <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>95828</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338985</v>
+        <v>339028</v>
       </c>
       <c r="R2" t="n">
-        <v>6394264</v>
+        <v>6394151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309429</v>
+        <v>122309061</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>95828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339028</v>
+        <v>338985</v>
       </c>
       <c r="R4" t="n">
-        <v>6394151</v>
+        <v>6394264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309226</v>
+        <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>95829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339035</v>
+        <v>338985</v>
       </c>
       <c r="R3" t="n">
-        <v>6394234</v>
+        <v>6394264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309061</v>
+        <v>122309226</v>
       </c>
       <c r="B4" t="n">
-        <v>95828</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338985</v>
+        <v>339035</v>
       </c>
       <c r="R4" t="n">
-        <v>6394264</v>
+        <v>6394234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309429</v>
+        <v>122309061</v>
       </c>
       <c r="B2" t="n">
-        <v>95012</v>
+        <v>95832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339028</v>
+        <v>338985</v>
       </c>
       <c r="R2" t="n">
-        <v>6394151</v>
+        <v>6394264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309061</v>
+        <v>122309226</v>
       </c>
       <c r="B3" t="n">
-        <v>95829</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338985</v>
+        <v>339035</v>
       </c>
       <c r="R3" t="n">
-        <v>6394264</v>
+        <v>6394234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309226</v>
+        <v>122309429</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>95015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339035</v>
+        <v>339028</v>
       </c>
       <c r="R4" t="n">
-        <v>6394234</v>
+        <v>6394151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309061</v>
+        <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>95832</v>
+        <v>95015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338985</v>
+        <v>339028</v>
       </c>
       <c r="R2" t="n">
-        <v>6394264</v>
+        <v>6394151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309429</v>
+        <v>122309061</v>
       </c>
       <c r="B4" t="n">
-        <v>95015</v>
+        <v>95832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339028</v>
+        <v>338985</v>
       </c>
       <c r="R4" t="n">
-        <v>6394151</v>
+        <v>6394264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122309429</v>
       </c>
       <c r="B2" t="n">
-        <v>95015</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309226</v>
+        <v>122309061</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
+          <t>Rågdal, Rågdal, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339035</v>
+        <v>338985</v>
       </c>
       <c r="R3" t="n">
-        <v>6394234</v>
+        <v>6394264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122309061</v>
+        <v>122309226</v>
       </c>
       <c r="B4" t="n">
-        <v>95832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rågdal, Rågdal, Vg</t>
+          <t>Rågdal, Härryda, Rågdal, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338985</v>
+        <v>339035</v>
       </c>
       <c r="R4" t="n">
-        <v>6394264</v>
+        <v>6394234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +974,7 @@
         <v>122355435</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16723-2023 artfynd.xlsx
+++ b/artfynd/A 16723-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122309429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122309061</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122309226</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122355435</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>